--- a/erp-server/erp-server-scm/src/main/resources/excel/purchaseOrderExport.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/purchaseOrderExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28125" windowHeight="11940"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>采购单号</t>
   </si>
@@ -42,6 +42,12 @@
     <t>计划交期</t>
   </si>
   <si>
+    <t>报关名称</t>
+  </si>
+  <si>
+    <t>报关型号</t>
+  </si>
+  <si>
     <t>交货仓库</t>
   </si>
   <si>
@@ -72,7 +78,7 @@
     <t>审核人（最新）</t>
   </si>
   <si>
-    <t>申请人</t>
+    <t>采购员</t>
   </si>
   <si>
     <t>创建人</t>
@@ -103,6 +109,12 @@
   </si>
   <si>
     <t>{.planDeliveryDate}</t>
+  </si>
+  <si>
+    <t>{.declareName}</t>
+  </si>
+  <si>
+    <t>{.declareModel}</t>
   </si>
   <si>
     <t>{.deliveryWarehouseName}</t>
@@ -154,14 +166,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -619,48 +624,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -670,97 +678,94 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1116,7 +1121,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -1124,15 +1129,15 @@
     <col min="4" max="4" width="10.375" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="7" max="7" width="10.375" customWidth="1"/>
-    <col min="8" max="8" width="9.625" customWidth="1"/>
-    <col min="9" max="9" width="10.125" customWidth="1"/>
-    <col min="10" max="10" width="10.375" customWidth="1"/>
-    <col min="18" max="18" width="14" customWidth="1"/>
-    <col min="19" max="19" width="10.25" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="8" max="10" width="9.625" customWidth="1"/>
+    <col min="11" max="11" width="10.125" customWidth="1"/>
+    <col min="12" max="12" width="10.375" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="10.25" customWidth="1"/>
+    <col min="22" max="22" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1196,70 +1201,82 @@
       <c r="U1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="T2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="U2" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="V2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
